--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -20734,6 +20734,154 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20767,7 +20915,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -20850,7 +20998,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -20860,7 +21008,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -20912,7 +21060,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33146</v>
+        <v>33147</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1454,9 +1451,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1602,9 +1596,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1998,9 +1989,6 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -3874,9 +3862,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4415,9 +4400,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4563,9 +4545,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4959,9 +4938,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -6687,9 +6663,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7228,9 +7201,6 @@
       <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -7376,9 +7346,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7772,9 +7739,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9352,9 +9316,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -9500,9 +9461,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="S55" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10041,9 +9999,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -10189,9 +10144,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -10585,9 +10537,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -12165,9 +12114,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -12313,9 +12259,6 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12854,9 +12797,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -13002,9 +12942,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -13398,9 +13335,6 @@
       <c r="O78" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -15274,9 +15208,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -15570,9 +15501,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -15718,9 +15646,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -16114,9 +16039,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -16510,9 +16432,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -16658,9 +16577,6 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -16806,9 +16722,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -16954,9 +16867,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -17102,9 +17012,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -17250,9 +17157,6 @@
       <c r="O102" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -17398,9 +17302,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -17546,9 +17447,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -17694,9 +17592,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -17842,9 +17737,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -17990,9 +17882,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -18386,9 +18275,6 @@
       <c r="O109" t="n">
         <v>2</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -18782,9 +18668,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -18930,9 +18813,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -19078,9 +18958,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -19226,9 +19103,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -19374,9 +19248,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -19522,9 +19393,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -19670,9 +19538,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -19818,9 +19683,6 @@
       <c r="O118" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -19966,9 +19828,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -20114,9 +19973,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -20262,9 +20118,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -20410,9 +20263,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -20805,9 +20655,6 @@
       </c>
       <c r="O124" t="n">
         <v>1</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>0.0008168084075657662</v>

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -15309,12 +15309,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -15348,84 +15348,92 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>7315</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>7315</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0.5177243301300694</v>
+        <v>0</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15460,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -15501,76 +15509,165 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary brucellosis notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
+        <v>1</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15602,12 +15699,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -15641,95 +15738,84 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>7315</v>
       </c>
       <c r="O93" t="n">
+        <v>7315</v>
+      </c>
+      <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>0.5177243301300694</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -15756,17 +15842,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -15805,165 +15891,76 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD94" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE94" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG94" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN94" t="b">
-        <v>1</v>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15995,12 +15992,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -16034,13 +16031,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -16049,7 +16046,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -16074,7 +16071,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -16087,42 +16084,42 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16154,12 +16151,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -16193,29 +16190,29 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Brucellos</t>
+          <t>Brucellose</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -16240,7 +16237,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
@@ -16275,17 +16272,17 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -16308,7 +16305,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -16321,42 +16318,42 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16388,12 +16385,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -16418,7 +16415,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -16427,81 +16424,95 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -16528,17 +16539,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -16563,7 +16574,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -16577,76 +16588,165 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="R98" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN98" t="b">
+        <v>1</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -16708,7 +16808,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -16853,7 +16953,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -16862,13 +16962,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -16998,7 +17098,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -17143,7 +17243,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -17152,13 +17252,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -17288,7 +17388,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -17433,7 +17533,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -17442,13 +17542,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -17548,12 +17648,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -17578,12 +17678,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -17626,42 +17726,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17693,12 +17793,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -17723,12 +17823,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N106" t="n">
@@ -17771,42 +17871,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -17838,12 +17938,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -17877,95 +17977,81 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17992,17 +18078,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18036,170 +18122,81 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG108" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN108" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18231,12 +18228,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -18270,13 +18267,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R109" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -18285,7 +18282,7 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -18310,7 +18307,7 @@
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT109" t="n">
@@ -18323,42 +18320,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18390,12 +18387,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -18429,29 +18426,29 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>Brucellos</t>
+          <t>Brucellose</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -18476,7 +18473,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
@@ -18511,17 +18508,17 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -18544,7 +18541,7 @@
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT110" t="n">
@@ -18557,42 +18554,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18624,12 +18621,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -18654,7 +18651,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -18663,81 +18660,95 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18764,17 +18775,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -18799,7 +18810,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -18808,81 +18819,170 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18944,7 +19044,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -19089,7 +19189,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -19098,13 +19198,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -19234,7 +19334,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -19379,7 +19479,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -19388,13 +19488,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -19524,7 +19624,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -19669,7 +19769,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -19678,13 +19778,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -19814,7 +19914,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -19929,12 +20029,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -19959,22 +20059,22 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -20007,42 +20107,42 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20074,12 +20174,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20104,12 +20204,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -20152,42 +20252,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20219,12 +20319,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20271,82 +20371,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20373,17 +20459,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -20422,165 +20508,76 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>1</v>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20612,118 +20609,511 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
         <is>
           <t>布鲁氏菌病</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="K126" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N124" t="n">
+      <c r="N126" t="n">
         <v>1</v>
       </c>
-      <c r="O124" t="n">
+      <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="R124" t="n">
+      <c r="R126" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S124" t="inlineStr">
+      <c r="S126" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO124" t="inlineStr">
+      <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP124" t="inlineStr">
+      <c r="AP126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR124" t="inlineStr">
+      <c r="AR126" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS124" t="inlineStr"/>
-      <c r="AT124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV124" t="inlineStr">
+      <c r="AV126" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW124" t="inlineStr">
+      <c r="AW126" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
+      <c r="AX126" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY124" t="inlineStr">
+      <c r="AY126" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
+      <c r="AZ126" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA124" t="inlineStr">
+      <c r="BA126" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB124" t="inlineStr">
+      <c r="BB126" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC124" t="inlineStr">
+      <c r="BC126" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -20845,7 +21235,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -20855,7 +21245,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -20875,7 +21265,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -21119,6 +21119,151 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21152,7 +21297,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -21235,7 +21380,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -21245,7 +21390,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -18083,12 +18083,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18122,13 +18122,16 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>6996</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>6996</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>2</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>0.4951468781394348</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -18161,42 +18164,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -18228,12 +18231,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -18267,95 +18270,81 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18382,7 +18371,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -18431,98 +18420,23 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
+      <c r="R110" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN110" t="b">
-        <v>1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -18616,17 +18530,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -18660,22 +18574,39 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>2</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0.01868976085656669</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -18683,6 +18614,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>1</v>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18700,7 +18689,7 @@
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT111" t="n">
@@ -18713,42 +18702,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18775,7 +18764,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -18824,98 +18813,23 @@
       <c r="O112" t="n">
         <v>2</v>
       </c>
+      <c r="R112" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Brucellos</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -19009,17 +18923,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -19044,7 +18958,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -19053,81 +18967,170 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19159,12 +19162,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -19237,42 +19240,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19304,12 +19307,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -19334,7 +19337,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -19382,42 +19385,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19449,12 +19452,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -19488,13 +19491,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -19527,42 +19530,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19594,12 +19597,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -19624,7 +19627,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -19633,13 +19636,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -19672,42 +19675,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19739,12 +19742,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -19817,42 +19820,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19884,12 +19887,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -19914,7 +19917,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -19962,42 +19965,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20029,12 +20032,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20068,13 +20071,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -20107,42 +20110,42 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20174,12 +20177,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20204,7 +20207,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -20213,13 +20216,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -20252,42 +20255,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20319,12 +20322,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20349,12 +20352,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N122" t="n">
@@ -20397,42 +20400,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20464,12 +20467,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -20542,42 +20545,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20609,12 +20612,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -20661,82 +20664,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20763,7 +20752,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -20812,98 +20801,23 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -20997,17 +20911,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21032,7 +20946,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -21041,81 +20955,170 @@
         </is>
       </c>
       <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
         <v>1</v>
       </c>
-      <c r="O126" t="n">
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
         <v>1</v>
       </c>
-      <c r="R126" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP126" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
-      <c r="AT126" t="n">
-        <v>0</v>
-      </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21177,7 +21180,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21186,13 +21189,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -21259,6 +21262,151 @@
         </is>
       </c>
       <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -21380,7 +21528,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -21390,7 +21538,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -21442,7 +21590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33147</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="16">
@@ -21452,7 +21600,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -21412,6 +21412,151 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21445,7 +21590,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -21528,7 +21673,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -21538,7 +21683,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -21590,7 +21735,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40143</v>
+        <v>40144</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -21554,6 +21554,151 @@
       <c r="BC129" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21590,7 +21735,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -21673,7 +21818,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -21683,7 +21828,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -21735,7 +21880,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40144</v>
+        <v>40145</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -21702,6 +21702,151 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21735,7 +21880,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -21818,7 +21963,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10">
@@ -21828,7 +21973,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -21880,7 +22025,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40145</v>
+        <v>40146</v>
       </c>
     </row>
     <row r="16">
